--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-kardiale-deviceimplantation.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-kardiale-deviceimplantation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Unknown region code '276'</t>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Procedure|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Procedure|2027.0.0-ballot</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -671,7 +671,7 @@
     <t>durchfuehrungsabsicht</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Durchfuehrungsabsicht|2027.0.0-ballot.rc1}
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/StructureDefinition/Durchfuehrungsabsicht|2027.0.0-ballot}
 </t>
   </si>
   <si>
@@ -699,7 +699,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-intend|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-intend|2027.0.0-ballot</t>
   </si>
   <si>
     <t>Procedure.extension:durchfuehrungsabsicht.value[x].id</t>
@@ -1067,7 +1067,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-category-sct|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-category-sct|2027.0.0-ballot</t>
   </si>
   <si>
     <t>Procedure.category.coding:sct.id</t>
@@ -1229,7 +1229,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-kardiale-deviceimplantation-ops|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-kardiale-deviceimplantation-ops|2027.0.0-ballot</t>
   </si>
   <si>
     <t>Procedure.code.coding:ops.id</t>
@@ -1370,7 +1370,7 @@
     <t>Procedure.code.coding:sct</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-kardiale-deviceimplantation-scnomedct|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-kardiale-deviceimplantation-scnomedct|2027.0.0-ballot</t>
   </si>
   <si>
     <t>Procedure.code.coding:sct.id</t>
@@ -1837,7 +1837,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite|5.3.0}
+    <t xml:space="preserve">Extension {bodySite|5.4.0}
 </t>
   </si>
   <si>
@@ -1881,7 +1881,7 @@
     <t>snomed-ct</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-kardiale-deviceimplantation-koerperstelle-snomedct|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-kardiale-deviceimplantation-koerperstelle-snomedct|2027.0.0-ballot</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding:snomed-ct.id</t>
@@ -2419,7 +2419,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="115.3046875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="112.296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2434,7 +2434,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="127.73046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="124.71875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-kardiale-deviceimplantation.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-kardiale-deviceimplantation.xlsx
@@ -2046,7 +2046,7 @@
     <t>Procedure.focalDevice.manipulated</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/StructureDefinition/mii-pr-kardio-device|2027.0.0-ballot)
 </t>
   </si>
   <si>
@@ -19221,7 +19221,7 @@
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G152" t="s" s="2">
         <v>78</v>
